--- a/warehouse_gui_server/데이터 베이스.xlsx
+++ b/warehouse_gui_server/데이터 베이스.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11835" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 

--- a/warehouse_gui_server/데이터 베이스.xlsx
+++ b/warehouse_gui_server/데이터 베이스.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11835" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -55,7 +55,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -63,6 +63,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -495,11 +498,11 @@
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>초코파이</t>
         </is>
       </c>
       <c r="D2" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -511,11 +514,11 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>새우깡</t>
         </is>
       </c>
       <c r="D3" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -527,11 +530,11 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>꿀꽈배기</t>
         </is>
       </c>
       <c r="D4" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -543,11 +546,11 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>맛동산</t>
         </is>
       </c>
       <c r="D5" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -559,11 +562,11 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>바나나킥</t>
         </is>
       </c>
       <c r="D6" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -575,11 +578,11 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>오징어땅콩</t>
         </is>
       </c>
       <c r="D7" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -591,11 +594,11 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>칸쵸</t>
         </is>
       </c>
       <c r="D8" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -607,11 +610,11 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>양파링</t>
         </is>
       </c>
       <c r="D9" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -623,11 +626,11 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>콘칩</t>
         </is>
       </c>
       <c r="D10" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -639,11 +642,11 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>프링글스</t>
         </is>
       </c>
       <c r="D11" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -655,11 +658,11 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>썬칩</t>
         </is>
       </c>
       <c r="D12" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -671,11 +674,11 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>오징어집</t>
         </is>
       </c>
       <c r="D13" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -687,11 +690,11 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>솔의눈</t>
         </is>
       </c>
       <c r="D14" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -703,11 +706,11 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>파워에이드</t>
         </is>
       </c>
       <c r="D15" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -719,11 +722,11 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>콜라</t>
         </is>
       </c>
       <c r="D16" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -735,11 +738,11 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>사이다</t>
         </is>
       </c>
       <c r="D17" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -751,11 +754,11 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>박카스</t>
         </is>
       </c>
       <c r="D18" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -767,11 +770,11 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>소주</t>
         </is>
       </c>
       <c r="D19" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -783,11 +786,11 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>맥주</t>
         </is>
       </c>
       <c r="D20" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -799,11 +802,11 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>오렌지주스</t>
         </is>
       </c>
       <c r="D21" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -815,11 +818,11 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>아침햇살</t>
         </is>
       </c>
       <c r="D22" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -831,11 +834,11 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>막걸리</t>
         </is>
       </c>
       <c r="D23" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -847,11 +850,11 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>레쓰비</t>
         </is>
       </c>
       <c r="D24" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -861,13 +864,13 @@
           <t>2-4-3</t>
         </is>
       </c>
-      <c r="C25" s="0" t="inlineStr">
-        <is>
-          <t>껌</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2%</t>
         </is>
       </c>
       <c r="D25" s="0" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
